--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(5).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(5).xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Projects\VNovelizerTest_v1.0\Assets\Resources\VNovelizerRes\ExcelVNScripts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -206,11 +211,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -219,7 +219,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>大卫线</t>
+      <t>sntzm_david313-315(6)</t>
     </r>
     <r>
       <rPr>
@@ -227,23 +227,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>313-315</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（最终分支）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_1, 1)</t>
+      <t>, 1)</t>
     </r>
   </si>
   <si>
